--- a/04_DESIGN_TABLES/DesignTable_5406_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5406_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF29"/>
+  <dimension ref="A1:AF32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,7 +795,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | thin wall 0.022 between the female thread and the male thread root (as printed)</t>
+          <t>thin wall 0.022 between the female thread and the male thread root (as printed)</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | thin wall 0.024 between the female thread and the male thread root (as printed)</t>
+          <t>thin wall 0.024 between the female thread and the male thread root (as printed)</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1151,83 +1151,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5406-12-02</t>
+          <t>5406-08-04</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.65241</v>
+        <v>0.50807</v>
       </c>
       <c r="D7" t="n">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="E7" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="G7" t="n">
         <v>1.7899</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2043</v>
+        <v>0.2163</v>
       </c>
       <c r="I7" t="n">
-        <v>1.02482</v>
+        <v>0.81557</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="K7" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="M7" t="n">
-        <v>0.45527</v>
+        <v>0.35064</v>
       </c>
       <c r="N7" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="O7" t="n">
-        <v>0.46</v>
+        <v>0.67</v>
       </c>
       <c r="P7" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.46</v>
+        <v>0.67</v>
       </c>
       <c r="R7" t="n">
-        <v>0.037</v>
+        <v>0.0556</v>
       </c>
       <c r="S7" t="n">
-        <v>0.165</v>
+        <v>0.215</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1946</v>
+        <v>0.2594</v>
       </c>
       <c r="U7" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="V7" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="W7" t="n">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>5406-12-02</t>
+          <t>5406-08-04</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 3/4-14 NPTF x 1/8-27 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1/2-14 NPTF x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1237,17 +1237,17 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>1/8-27 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1255,92 +1255,97 @@
           <t>Air-Way s86 only (double-pass 31 rows); female NPTF per ANSI B1.20.3, tap drill tabulated | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION), hex head behind it; female NPTF port from the hex face: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table), helical thread over P1; Brennan 5405-08-08 STEP confirms the P1 rule for 1/2 NPTF (VERIFIED -08 only); Air-Way publishes no through-bore for the bushing -&gt; the tap drill is carried through to the male tip (ASSUMPTION, machined-bushing practice); wall between the female thread crests and the male thread roots checked per row</t>
         </is>
       </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p013-t01: agrees on L2@DRIVE, C2HEX@HEX, TAPDRILL@BORE</t>
+        </is>
+      </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>5406-12-02</t>
+          <t>5406-08-04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5406-12-04</t>
+          <t>5406-08-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.65241</v>
+        <v>0.50807</v>
       </c>
       <c r="D8" t="n">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="E8" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="G8" t="n">
         <v>1.7899</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2043</v>
+        <v>0.2163</v>
       </c>
       <c r="I8" t="n">
-        <v>1.02482</v>
+        <v>0.81557</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="K8" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="M8" t="n">
-        <v>0.45527</v>
+        <v>0.35064</v>
       </c>
       <c r="N8" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="O8" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="P8" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="R8" t="n">
         <v>0.0556</v>
       </c>
       <c r="S8" t="n">
-        <v>0.215</v>
+        <v>0.285</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2594</v>
+        <v>0.3294</v>
       </c>
       <c r="U8" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5406-12-04</t>
+          <t>5406-08-06</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 3/4-14 NPTF x 1/4-18 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1/2-14 NPTF x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1350,17 +1355,17 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1368,16 +1373,21 @@
           <t>Air-Way s86 only (double-pass 31 rows); female NPTF per ANSI B1.20.3, tap drill tabulated | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION), hex head behind it; female NPTF port from the hex face: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table), helical thread over P1; Brennan 5405-08-08 STEP confirms the P1 rule for 1/2 NPTF (VERIFIED -08 only); Air-Way publishes no through-bore for the bushing -&gt; the tap drill is carried through to the male tip (ASSUMPTION, machined-bushing practice); wall between the female thread crests and the male thread roots checked per row</t>
         </is>
       </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p013-t01: agrees on L2@DRIVE, C2HEX@HEX, TAPDRILL@BORE | thin wall 0.021 between the female thread and the male thread root (as printed)</t>
+        </is>
+      </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>5406-12-04</t>
+          <t>5406-08-06</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5406-12-06</t>
+          <t>5406-12-02</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1417,43 +1427,43 @@
         <v>0.45527</v>
       </c>
       <c r="N9" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="O9" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="P9" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0556</v>
+        <v>0.037</v>
       </c>
       <c r="S9" t="n">
-        <v>0.285</v>
+        <v>0.165</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3294</v>
+        <v>0.1946</v>
       </c>
       <c r="U9" t="n">
         <v>1.17</v>
       </c>
       <c r="V9" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="W9" t="n">
-        <v>0.49</v>
+        <v>0.71</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5406-12-06</t>
+          <t>5406-12-02</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 3/4-14 NPTF x 3/8-18 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 3/4-14 NPTF x 1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1468,7 +1478,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1483,14 +1493,14 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>5406-12-06</t>
+          <t>5406-12-02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5406-12-08</t>
+          <t>5406-12-04</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1530,43 +1540,43 @@
         <v>0.45527</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="R10" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="S10" t="n">
-        <v>0.35</v>
+        <v>0.215</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4071</v>
+        <v>0.2594</v>
       </c>
       <c r="U10" t="n">
         <v>1.17</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="W10" t="n">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>5406-12-08</t>
+          <t>5406-12-04</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 3/4-14 NPTF x 1/2-14 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 3/4-14 NPTF x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1581,7 +1591,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1596,90 +1606,90 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>5406-12-08</t>
+          <t>5406-12-04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5406-16-02</t>
+          <t>5406-12-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="C11" t="n">
-        <v>0.79674</v>
+        <v>0.65241</v>
       </c>
       <c r="D11" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="G11" t="n">
         <v>1.7899</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2572</v>
+        <v>0.2043</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2832</v>
+        <v>1.02482</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="K11" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="M11" t="n">
-        <v>0.57203</v>
+        <v>0.45527</v>
       </c>
       <c r="N11" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="O11" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="P11" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="R11" t="n">
-        <v>0.037</v>
+        <v>0.0556</v>
       </c>
       <c r="S11" t="n">
-        <v>0.165</v>
+        <v>0.285</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1946</v>
+        <v>0.3294</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="W11" t="n">
-        <v>0.9</v>
+        <v>0.49</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>5406-16-02</t>
+          <t>5406-12-06</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1-11 1/2 NPTF x 1/8-27 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 3/4-14 NPTF x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1689,12 +1699,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>1/8-27 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1709,90 +1719,90 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>5406-16-02</t>
+          <t>5406-12-06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5406-16-04</t>
+          <t>5406-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="C12" t="n">
-        <v>0.79674</v>
+        <v>0.65241</v>
       </c>
       <c r="D12" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="G12" t="n">
         <v>1.7899</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2572</v>
+        <v>0.2043</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2832</v>
+        <v>1.02482</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="K12" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="M12" t="n">
-        <v>0.57203</v>
+        <v>0.45527</v>
       </c>
       <c r="N12" t="n">
-        <v>0.43</v>
+        <v>0.7</v>
       </c>
       <c r="O12" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="P12" t="n">
-        <v>0.43</v>
+        <v>0.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0556</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>0.215</v>
+        <v>0.35</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2594</v>
+        <v>0.4071</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>0.43</v>
+        <v>0.7</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5406-16-04</t>
+          <t>5406-12-08</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1-11 1/2 NPTF x 1/4-18 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 3/4-14 NPTF x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1802,12 +1812,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1822,14 +1832,14 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>5406-16-04</t>
+          <t>5406-12-08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5406-16-06</t>
+          <t>5406-16-02</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1869,43 +1879,43 @@
         <v>0.57203</v>
       </c>
       <c r="N13" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="O13" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="P13" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0556</v>
+        <v>0.037</v>
       </c>
       <c r="S13" t="n">
-        <v>0.285</v>
+        <v>0.165</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3294</v>
+        <v>0.1946</v>
       </c>
       <c r="U13" t="n">
         <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="W13" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>5406-16-06</t>
+          <t>5406-16-02</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1-11 1/2 NPTF x 3/8-18 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1-11 1/2 NPTF x 1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -1920,7 +1930,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1935,14 +1945,14 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>5406-16-06</t>
+          <t>5406-16-02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5406-16-12</t>
+          <t>5406-16-04</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1982,43 +1992,43 @@
         <v>0.57203</v>
       </c>
       <c r="N14" t="n">
-        <v>0.91</v>
+        <v>0.43</v>
       </c>
       <c r="O14" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="P14" t="n">
-        <v>0.91</v>
+        <v>0.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="R14" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="S14" t="n">
-        <v>0.455</v>
+        <v>0.215</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5121</v>
+        <v>0.2594</v>
       </c>
       <c r="U14" t="n">
         <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0.91</v>
+        <v>0.43</v>
       </c>
       <c r="W14" t="n">
-        <v>0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>5406-16-12</t>
+          <t>5406-16-04</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1-11 1/2 NPTF x 3/4-14 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1-11 1/2 NPTF x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2033,7 +2043,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2048,90 +2058,90 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>5406-16-12</t>
+          <t>5406-16-04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5406-20-04</t>
+          <t>5406-16-06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="C15" t="n">
-        <v>1.01036</v>
+        <v>0.79674</v>
       </c>
       <c r="D15" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="E15" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="G15" t="n">
         <v>1.7899</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2632</v>
+        <v>0.2572</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6267</v>
+        <v>1.2832</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="K15" t="n">
         <v>0.08696</v>
       </c>
       <c r="L15" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>0.74378</v>
+        <v>0.57203</v>
       </c>
       <c r="N15" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="O15" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="P15" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="R15" t="n">
         <v>0.0556</v>
       </c>
       <c r="S15" t="n">
-        <v>0.215</v>
+        <v>0.285</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2594</v>
+        <v>0.3294</v>
       </c>
       <c r="U15" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>5406-20-04</t>
+          <t>5406-16-06</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/4-11 1/2 NPTF x 1/4-18 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1-11 1/2 NPTF x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2141,12 +2151,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2161,90 +2171,90 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>5406-20-04</t>
+          <t>5406-16-06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5406-20-06</t>
+          <t>5406-16-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="C16" t="n">
-        <v>1.01036</v>
+        <v>0.79674</v>
       </c>
       <c r="D16" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="E16" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="G16" t="n">
         <v>1.7899</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2632</v>
+        <v>0.2572</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6267</v>
+        <v>1.2832</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="K16" t="n">
         <v>0.08696</v>
       </c>
       <c r="L16" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.74378</v>
+        <v>0.57203</v>
       </c>
       <c r="N16" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="O16" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="P16" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0556</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>0.285</v>
+        <v>0.455</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3294</v>
+        <v>0.5121</v>
       </c>
       <c r="U16" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="W16" t="n">
-        <v>0.79</v>
+        <v>0.45</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>5406-20-06</t>
+          <t>5406-16-12</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/4-11 1/2 NPTF x 3/8-18 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1-11 1/2 NPTF x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2254,12 +2264,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2274,14 +2284,14 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>5406-20-06</t>
+          <t>5406-16-12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5406-20-08</t>
+          <t>5406-20-04</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2321,43 +2331,43 @@
         <v>0.74378</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="R17" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="S17" t="n">
-        <v>0.35</v>
+        <v>0.215</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4071</v>
+        <v>0.2594</v>
       </c>
       <c r="U17" t="n">
         <v>1.47</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="W17" t="n">
-        <v>0.57</v>
+        <v>0.8</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>5406-20-08</t>
+          <t>5406-20-04</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/4-11 1/2 NPTF x 1/2-14 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/4-11 1/2 NPTF x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2372,7 +2382,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2387,14 +2397,14 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>5406-20-08</t>
+          <t>5406-20-04</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5406-20-12</t>
+          <t>5406-20-06</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2434,43 +2444,43 @@
         <v>0.74378</v>
       </c>
       <c r="N18" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="O18" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="P18" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="R18" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="S18" t="n">
-        <v>0.455</v>
+        <v>0.285</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5121</v>
+        <v>0.3294</v>
       </c>
       <c r="U18" t="n">
         <v>1.47</v>
       </c>
       <c r="V18" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>5406-20-12</t>
+          <t>5406-20-06</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/4-11 1/2 NPTF x 3/4-14 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/4-11 1/2 NPTF x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2485,7 +2495,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2500,14 +2510,14 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>5406-20-12</t>
+          <t>5406-20-06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5406-20-16</t>
+          <t>5406-20-08</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2547,43 +2557,43 @@
         <v>0.74378</v>
       </c>
       <c r="N19" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="P19" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="R19" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.4071</v>
       </c>
       <c r="U19" t="n">
         <v>1.47</v>
       </c>
       <c r="V19" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="W19" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>5406-20-16</t>
+          <t>5406-20-08</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/4-11 1/2 NPTF x 1-11 1/2 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/4-11 1/2 NPTF x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2598,7 +2608,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2613,90 +2623,90 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>5406-20-16</t>
+          <t>5406-20-08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5406-24-04</t>
+          <t>5406-20-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1547</v>
+        <v>1.01036</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="E20" t="n">
-        <v>0.93283</v>
+        <v>0.81335</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7235</v>
+        <v>0.7068</v>
       </c>
       <c r="G20" t="n">
         <v>1.7899</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2765</v>
+        <v>0.2632</v>
       </c>
       <c r="I20" t="n">
-        <v>1.86566</v>
+        <v>1.6267</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7235</v>
+        <v>0.7068</v>
       </c>
       <c r="K20" t="n">
         <v>0.08696</v>
       </c>
       <c r="L20" t="n">
-        <v>0.93283</v>
+        <v>0.81335</v>
       </c>
       <c r="M20" t="n">
-        <v>0.86326</v>
+        <v>0.74378</v>
       </c>
       <c r="N20" t="n">
-        <v>0.43</v>
+        <v>0.91</v>
       </c>
       <c r="O20" t="n">
-        <v>0.67</v>
+        <v>0.91</v>
       </c>
       <c r="P20" t="n">
-        <v>0.43</v>
+        <v>0.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.67</v>
+        <v>0.91</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0556</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>0.215</v>
+        <v>0.455</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2594</v>
+        <v>0.5121</v>
       </c>
       <c r="U20" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="V20" t="n">
-        <v>0.43</v>
+        <v>0.91</v>
       </c>
       <c r="W20" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>5406-24-04</t>
+          <t>5406-20-12</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/2-11 1/2 NPTF x 1/4-18 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/4-11 1/2 NPTF x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2706,12 +2716,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2726,90 +2736,90 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>5406-24-04</t>
+          <t>5406-20-12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5406-24-08</t>
+          <t>5406-20-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="C21" t="n">
-        <v>1.1547</v>
+        <v>1.01036</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="E21" t="n">
-        <v>0.93283</v>
+        <v>0.81335</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7235</v>
+        <v>0.7068</v>
       </c>
       <c r="G21" t="n">
         <v>1.7899</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2765</v>
+        <v>0.2632</v>
       </c>
       <c r="I21" t="n">
-        <v>1.86566</v>
+        <v>1.6267</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7235</v>
+        <v>0.7068</v>
       </c>
       <c r="K21" t="n">
         <v>0.08696</v>
       </c>
       <c r="L21" t="n">
-        <v>0.93283</v>
+        <v>0.81335</v>
       </c>
       <c r="M21" t="n">
-        <v>0.86326</v>
+        <v>0.74378</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="R21" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>0.35</v>
+        <v>0.57</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4071</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="W21" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>5406-24-08</t>
+          <t>5406-20-16</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/2-11 1/2 NPTF x 1/2-14 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/4-11 1/2 NPTF x 1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2819,12 +2829,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2839,18 +2849,18 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>5406-24-08</t>
+          <t>5406-20-16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5406-24-12</t>
+          <t>5406-24-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="C22" t="n">
         <v>1.1547</v>
@@ -2886,43 +2896,43 @@
         <v>0.86326</v>
       </c>
       <c r="N22" t="n">
-        <v>0.91</v>
+        <v>0.43</v>
       </c>
       <c r="O22" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="P22" t="n">
-        <v>0.91</v>
+        <v>0.43</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="R22" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="S22" t="n">
-        <v>0.455</v>
+        <v>0.215</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5121</v>
+        <v>0.2594</v>
       </c>
       <c r="U22" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V22" t="n">
-        <v>0.91</v>
+        <v>0.43</v>
       </c>
       <c r="W22" t="n">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>5406-24-12</t>
+          <t>5406-24-04</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/2-11 1/2 NPTF x 3/4-14 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/2-11 1/2 NPTF x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -2937,7 +2947,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -2952,14 +2962,14 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>5406-24-12</t>
+          <t>5406-24-04</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5406-24-16</t>
+          <t>5406-24-08</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2999,43 +3009,43 @@
         <v>0.86326</v>
       </c>
       <c r="N23" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="P23" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="R23" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.4071</v>
       </c>
       <c r="U23" t="n">
         <v>1.57</v>
       </c>
       <c r="V23" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="W23" t="n">
-        <v>0.43</v>
+        <v>0.67</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>5406-24-16</t>
+          <t>5406-24-08</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/2-11 1/2 NPTF x 1-11 1/2 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/2-11 1/2 NPTF x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3050,7 +3060,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3065,14 +3075,14 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>5406-24-16</t>
+          <t>5406-24-08</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5406-24-20</t>
+          <t>5406-24-12</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -3112,43 +3122,43 @@
         <v>0.86326</v>
       </c>
       <c r="N24" t="n">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="O24" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="P24" t="n">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="R24" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>0.74</v>
+        <v>0.455</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8096</v>
+        <v>0.5121</v>
       </c>
       <c r="U24" t="n">
         <v>1.57</v>
       </c>
       <c r="V24" t="n">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="W24" t="n">
-        <v>0.41</v>
+        <v>0.66</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>5406-24-20</t>
+          <t>5406-24-12</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/2-11 1/2 NPTF x 1 1/4-11 1/2 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/2-11 1/2 NPTF x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3163,7 +3173,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3178,90 +3188,90 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>5406-24-20</t>
+          <t>5406-24-12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5406-32-08</t>
+          <t>5406-24-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="C25" t="n">
-        <v>1.44338</v>
+        <v>1.1547</v>
       </c>
       <c r="D25" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>1.16929</v>
+        <v>0.93283</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7565</v>
+        <v>0.7235</v>
       </c>
       <c r="G25" t="n">
         <v>1.7899</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2735</v>
+        <v>0.2765</v>
       </c>
       <c r="I25" t="n">
-        <v>2.33859</v>
+        <v>1.86566</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7565</v>
+        <v>0.7235</v>
       </c>
       <c r="K25" t="n">
         <v>0.08696</v>
       </c>
       <c r="L25" t="n">
-        <v>1.16929</v>
+        <v>0.93283</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09973</v>
+        <v>0.86326</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="R25" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>0.35</v>
+        <v>0.57</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4071</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="V25" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="W25" t="n">
-        <v>0.85</v>
+        <v>0.43</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>5406-32-08</t>
+          <t>5406-24-16</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 2-11 1/2 NPTF x 1/2-14 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/2-11 1/2 NPTF x 1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3271,12 +3281,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2-11 1/2 NPTF</t>
+          <t>1 1/2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3291,90 +3301,90 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>5406-32-08</t>
+          <t>5406-24-16</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5406-32-12</t>
+          <t>5406-24-20</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="C26" t="n">
-        <v>1.44338</v>
+        <v>1.1547</v>
       </c>
       <c r="D26" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>1.16929</v>
+        <v>0.93283</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7565</v>
+        <v>0.7235</v>
       </c>
       <c r="G26" t="n">
         <v>1.7899</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2735</v>
+        <v>0.2765</v>
       </c>
       <c r="I26" t="n">
-        <v>2.33859</v>
+        <v>1.86566</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7565</v>
+        <v>0.7235</v>
       </c>
       <c r="K26" t="n">
         <v>0.08696</v>
       </c>
       <c r="L26" t="n">
-        <v>1.16929</v>
+        <v>0.93283</v>
       </c>
       <c r="M26" t="n">
-        <v>1.09973</v>
+        <v>0.86326</v>
       </c>
       <c r="N26" t="n">
-        <v>0.91</v>
+        <v>1.48</v>
       </c>
       <c r="O26" t="n">
-        <v>0.91</v>
+        <v>1.16</v>
       </c>
       <c r="P26" t="n">
-        <v>0.91</v>
+        <v>1.48</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.91</v>
+        <v>1.16</v>
       </c>
       <c r="R26" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>0.455</v>
+        <v>0.74</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5121</v>
+        <v>0.8096</v>
       </c>
       <c r="U26" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="V26" t="n">
-        <v>0.91</v>
+        <v>1.48</v>
       </c>
       <c r="W26" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>5406-32-12</t>
+          <t>5406-24-20</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 2-11 1/2 NPTF x 3/4-14 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 1 1/2-11 1/2 NPTF x 1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3384,12 +3394,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2-11 1/2 NPTF</t>
+          <t>1 1/2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3404,14 +3414,14 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>5406-32-12</t>
+          <t>5406-24-20</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5406-32-16</t>
+          <t>5406-32-04</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -3451,43 +3461,43 @@
         <v>1.09973</v>
       </c>
       <c r="N27" t="n">
-        <v>1.14</v>
+        <v>0.43</v>
       </c>
       <c r="O27" t="n">
-        <v>1.14</v>
+        <v>0.67</v>
       </c>
       <c r="P27" t="n">
-        <v>1.14</v>
+        <v>0.43</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.14</v>
+        <v>0.67</v>
       </c>
       <c r="R27" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0556</v>
       </c>
       <c r="S27" t="n">
-        <v>0.57</v>
+        <v>0.215</v>
       </c>
       <c r="T27" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.2594</v>
       </c>
       <c r="U27" t="n">
         <v>1.75</v>
       </c>
       <c r="V27" t="n">
-        <v>1.14</v>
+        <v>0.43</v>
       </c>
       <c r="W27" t="n">
-        <v>0.61</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>5406-32-16</t>
+          <t>5406-32-04</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 2-11 1/2 NPTF x 1-11 1/2 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 2-11 1/2 NPTF x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3502,7 +3512,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3512,19 +3522,24 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Air-Way s86 only (double-pass 31 rows); female NPTF per ANSI B1.20.3, tap drill tabulated | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION), hex head behind it; female NPTF port from the hex face: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table), helical thread over P1; Brennan 5405-08-08 STEP confirms the P1 rule for 1/2 NPTF (VERIFIED -08 only); Air-Way publishes no through-bore for the bushing -&gt; the tap drill is carried through to the male tip (ASSUMPTION, machined-bushing practice); wall between the female thread crests and the male thread roots checked per row</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L2@DRIVE: Brennan TFA catalog p13 table TFA-p013-t01 "5406 MP-FP REDUCER BUSHING" row 5406-32-04 col "L LGTH" = "1.750" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 446.2, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p13 5406 drawing: L = overall, C HEX = bushing hex (impact/F2b.json, certain); A1 DRILL is NOT a printed tap drill (likely only); same-table check on today's base: 30/31 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5406-24-04 1.55 vs 1.57); C2HEX@HEX: Brennan TFA catalog p13 table TFA-p013-t01 "5406 MP-FP REDUCER BUSHING" row 5406-32-04 col "C HEX" = "2.500" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 446.2, page verified) [Brennan = yes 2026-10-18] - bushing hex; mapping: TFA p13 5406 drawing: L = overall, C HEX = bushing hex (impact/F2b.json, certain); A1 DRILL is NOT a printed tap drill (likely only); same-table check on today's base: 31/31 rows with an Air-Way/OMi value agree with this catalog column to rounding; TAPDRILL@BORE: end library gen_straight2 FPT[4] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.43, FPT_P1 0.67 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; the catalog A1 DRILL 0.431 is the male-end drill, not a printed tap drill (impact/F2b.json: likely only) - not used; THDMAJ_A2@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (female end); THDMAJ_A1@DRIVE: end library: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (male end); $PRP@Threads: thread texts from the part-number dashes, format of the built 5406 rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION), hex head behind it; female NPTF port from the hex face: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table), helical thread over P1; Brennan 5405-08-08 STEP confirms the P1 rule for 1/2 NPTF (VERIFIED -08 only); Air-Way publishes no through-bore for the bushing -&gt; the tap drill is carried through to the male tip (ASSUMPTION, machined-bushing practice); wall between the female thread crests and the male thread roots checked per row</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L2 / hex from the Brennan TFA catalog p13 alone; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>5406-32-16</t>
+          <t>5406-32-04</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5406-32-20</t>
+          <t>5406-32-08</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -3564,43 +3579,43 @@
         <v>1.09973</v>
       </c>
       <c r="N28" t="n">
-        <v>1.48</v>
+        <v>0.7</v>
       </c>
       <c r="O28" t="n">
-        <v>1.16</v>
+        <v>0.9</v>
       </c>
       <c r="P28" t="n">
-        <v>1.48</v>
+        <v>0.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.16</v>
+        <v>0.9</v>
       </c>
       <c r="R28" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>0.74</v>
+        <v>0.35</v>
       </c>
       <c r="T28" t="n">
-        <v>0.8096</v>
+        <v>0.4071</v>
       </c>
       <c r="U28" t="n">
         <v>1.75</v>
       </c>
       <c r="V28" t="n">
-        <v>1.48</v>
+        <v>0.7</v>
       </c>
       <c r="W28" t="n">
-        <v>0.59</v>
+        <v>0.85</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>5406-32-20</t>
+          <t>5406-32-08</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 2-11 1/2 NPTF x 1 1/4-11 1/2 NPTF (female)</t>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 2-11 1/2 NPTF x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -3615,7 +3630,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3630,14 +3645,14 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>5406-32-20</t>
+          <t>5406-32-08</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5406-32-24</t>
+          <t>5406-32-12</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -3677,71 +3692,410 @@
         <v>1.09973</v>
       </c>
       <c r="N29" t="n">
-        <v>1.72</v>
+        <v>0.91</v>
       </c>
       <c r="O29" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="P29" t="n">
-        <v>1.72</v>
+        <v>0.91</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="R29" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S29" t="n">
-        <v>0.86</v>
+        <v>0.455</v>
       </c>
       <c r="T29" t="n">
-        <v>0.9296</v>
+        <v>0.5121</v>
       </c>
       <c r="U29" t="n">
         <v>1.75</v>
       </c>
       <c r="V29" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>5406-32-12</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 2-11 1/2 NPTF x 3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>5406</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Air-Way s86 only (double-pass 31 rows); female NPTF per ANSI B1.20.3, tap drill tabulated | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION), hex head behind it; female NPTF port from the hex face: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table), helical thread over P1; Brennan 5405-08-08 STEP confirms the P1 rule for 1/2 NPTF (VERIFIED -08 only); Air-Way publishes no through-bore for the bushing -&gt; the tap drill is carried through to the male tip (ASSUMPTION, machined-bushing practice); wall between the female thread crests and the male thread roots checked per row</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>5406-32-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>5406-32-16</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.44338</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.6395999999999999</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>5406-32-16</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 2-11 1/2 NPTF x 1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>5406</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Air-Way s86 only (double-pass 31 rows); female NPTF per ANSI B1.20.3, tap drill tabulated | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION), hex head behind it; female NPTF port from the hex face: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table), helical thread over P1; Brennan 5405-08-08 STEP confirms the P1 rule for 1/2 NPTF (VERIFIED -08 only); Air-Way publishes no through-bore for the bushing -&gt; the tap drill is carried through to the male tip (ASSUMPTION, machined-bushing practice); wall between the female thread crests and the male thread roots checked per row</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>5406-32-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>5406-32-20</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.44338</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>5406-32-20</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 2-11 1/2 NPTF x 1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>5406</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Air-Way s86 only (double-pass 31 rows); female NPTF per ANSI B1.20.3, tap drill tabulated | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION), hex head behind it; female NPTF port from the hex face: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table), helical thread over P1; Brennan 5405-08-08 STEP confirms the P1 rule for 1/2 NPTF (VERIFIED -08 only); Air-Way publishes no through-bore for the bushing -&gt; the tap drill is carried through to the male tip (ASSUMPTION, machined-bushing practice); wall between the female thread crests and the male thread roots checked per row</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>5406-32-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5406-32-24</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.44338</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="N32" t="n">
         <v>1.72</v>
       </c>
-      <c r="W29" t="n">
+      <c r="O32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.9296</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W32" t="n">
         <v>0.59</v>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>5406-32-24</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Pipe Reducer Bushing (male NPTF x female NPTF), 2-11 1/2 NPTF x 1 1/2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>5406</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>1 1/2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>Air-Way s86 only (double-pass 31 rows); female NPTF per ANSI B1.20.3, tap drill tabulated | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION), hex head behind it; female NPTF port from the hex face: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table), helical thread over P1; Brennan 5405-08-08 STEP confirms the P1 rule for 1/2 NPTF (VERIFIED -08 only); Air-Way publishes no through-bore for the bushing -&gt; the tap drill is carried through to the male tip (ASSUMPTION, machined-bushing practice); wall between the female thread crests and the male thread roots checked per row</t>
         </is>
       </c>
-      <c r="AF29" t="inlineStr">
+      <c r="AF32" t="inlineStr">
         <is>
           <t>5406-32-24</t>
         </is>
